--- a/moduli_aziende/aifecs/moduli_compilati/MOD-720-G-Piano_Formazione_Annuale.xlsx
+++ b/moduli_aziende/aifecs/moduli_compilati/MOD-720-G-Piano_Formazione_Annuale.xlsx
@@ -2,26 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R370c20a722bf4797"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Red7fb258b5854a41"/>
   </x:sheets>
 </x:workbook>
-</file>
-
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:authors>
-    <x:author/>
-  </x:authors>
-  <x:commentList>
-    <x:comment ref="A1" authorId="0">
-      <x:text>
-        <x:r>
-          <x:t>AIFECS — BOZZA DA CONFERMARE. Proposta operativa per il sistema qualità ISO 9001. Ruoli, priorità, criteri e obiettivi sono proposte. I registri vanno compilati con dati ed evidenze reali. Vedere la guida e la proposta operativa del pacchetto.</x:t>
-        </x:r>
-      </x:text>
-    </x:comment>
-  </x:commentList>
-</x:comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -356,9 +339,7 @@
       <x:c r="H2" s="6" t="str">
         <x:v>Controllo pratiche e applicazione istruzioni</x:v>
       </x:c>
-      <x:c r="I2" s="5" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="I2" s="5"/>
     </x:row>
     <x:row r="3" ht="50" customHeight="1">
       <x:c r="A3" s="5"/>
@@ -381,9 +362,7 @@
       <x:c r="H3" s="6" t="str">
         <x:v>Riesame di un progetto didattico</x:v>
       </x:c>
-      <x:c r="I3" s="5" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="I3" s="5"/>
     </x:row>
     <x:row r="4" ht="50" customHeight="1">
       <x:c r="A4" s="5"/>
@@ -406,9 +385,7 @@
       <x:c r="H4" s="6" t="str">
         <x:v>Simulazione assistenza e gestione interruzione</x:v>
       </x:c>
-      <x:c r="I4" s="5" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="I4" s="5"/>
     </x:row>
     <x:row r="5" ht="50" customHeight="1">
       <x:c r="A5" s="5"/>
@@ -431,9 +408,7 @@
       <x:c r="H5" s="6" t="str">
         <x:v>Verifica campione fascicolo completo</x:v>
       </x:c>
-      <x:c r="I5" s="5" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="I5" s="5"/>
     </x:row>
     <x:row r="6" ht="50" customHeight="1">
       <x:c r="A6" s="5"/>
@@ -456,9 +431,7 @@
       <x:c r="H6" s="6" t="str">
         <x:v>Analisi caso e verifica trattamento</x:v>
       </x:c>
-      <x:c r="I6" s="5" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="I6" s="5"/>
     </x:row>
     <x:row r="7" ht="68" customHeight="1">
       <x:c r="A7" s="5"/>
@@ -481,9 +454,7 @@
       <x:c r="H7" s="6" t="str">
         <x:v>Verifica corretta applicazione accessi e versioni</x:v>
       </x:c>
-      <x:c r="I7" s="5" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="I7" s="5"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8"/>
@@ -528,6 +499,5 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b6927af74e045d1"/>
 </x:worksheet>
 </file>